--- a/artfynd/A 11553-2024 artfynd.xlsx
+++ b/artfynd/A 11553-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,49 +680,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128369925</v>
+        <v>136859183</v>
       </c>
       <c r="B2" t="n">
-        <v>93197</v>
+        <v>96565</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>2812</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gustavsnäs, Jmt</t>
+          <t>Mörtsjön, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>545958</v>
+        <v>546147</v>
       </c>
       <c r="R2" t="n">
-        <v>6960440</v>
+        <v>6960436</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -749,12 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,13 +786,1267 @@
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/136859183</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>136859192</v>
+      </c>
+      <c r="B3" t="n">
+        <v>96565</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>2812</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Kransmossa</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Hylocomiadelphus triquetrus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Mörtsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>546110</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6960425</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>08:37</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>08:37</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136859192</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>128369925</v>
+      </c>
+      <c r="B4" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Gustavsnäs, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>545958</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6960440</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/128369925</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>136859185</v>
+      </c>
+      <c r="B5" t="n">
+        <v>93083</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Mörtsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>546144</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6960426</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136859185</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>136859190</v>
+      </c>
+      <c r="B6" t="n">
+        <v>93083</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Mörtsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>546132</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6960426</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>08:32</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>08:32</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136859190</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>136859191</v>
+      </c>
+      <c r="B7" t="n">
+        <v>93083</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Mörtsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>546122</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6960432</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>08:34</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>08:34</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136859191</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>136859196</v>
+      </c>
+      <c r="B8" t="n">
+        <v>93083</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Mörtsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>546101</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6960427</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136859196</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>136859193</v>
+      </c>
+      <c r="B9" t="n">
+        <v>93447</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Mörtsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>546111</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6960415</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>08:59</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>08:59</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Kalkpåverkad mark</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136859193</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>136859173</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79476</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Mörtsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>546190</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6960431</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>07:33</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>07:33</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136859173</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>136859199</v>
+      </c>
+      <c r="B11" t="n">
+        <v>58169</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Mörtsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>545964</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6960465</v>
+      </c>
+      <c r="S11" t="n">
+        <v>8</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>09:12</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>09:12</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136859199</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>136859184</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99691</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>219880</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Kransrams</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Polygonatum verticillatum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Mörtsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>546146</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6960434</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>08:29</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>08:29</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136859184</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>136859187</v>
+      </c>
+      <c r="B13" t="n">
+        <v>104876</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Mörtsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>546141</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6960424</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136859187</t>
         </is>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 11553-2024 artfynd.xlsx
+++ b/artfynd/A 11553-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136859183</v>
       </c>
       <c r="B2" t="n">
-        <v>96565</v>
+        <v>96571</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136859192</v>
       </c>
       <c r="B3" t="n">
-        <v>96565</v>
+        <v>96571</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136859185</v>
       </c>
       <c r="B5" t="n">
-        <v>93083</v>
+        <v>93085</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>136859190</v>
       </c>
       <c r="B6" t="n">
-        <v>93083</v>
+        <v>93085</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1245,7 +1245,7 @@
         <v>136859191</v>
       </c>
       <c r="B7" t="n">
-        <v>93083</v>
+        <v>93085</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         <v>136859196</v>
       </c>
       <c r="B8" t="n">
-        <v>93083</v>
+        <v>93085</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>136859193</v>
       </c>
       <c r="B9" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>136859173</v>
       </c>
       <c r="B10" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>136859184</v>
       </c>
       <c r="B12" t="n">
-        <v>99691</v>
+        <v>99697</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
         <v>136859187</v>
       </c>
       <c r="B13" t="n">
-        <v>104876</v>
+        <v>104882</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 11553-2024 artfynd.xlsx
+++ b/artfynd/A 11553-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136859183</v>
       </c>
       <c r="B2" t="n">
-        <v>96571</v>
+        <v>96573</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136859192</v>
       </c>
       <c r="B3" t="n">
-        <v>96571</v>
+        <v>96573</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136859185</v>
       </c>
       <c r="B5" t="n">
-        <v>93085</v>
+        <v>93087</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>136859190</v>
       </c>
       <c r="B6" t="n">
-        <v>93085</v>
+        <v>93087</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1245,7 +1245,7 @@
         <v>136859191</v>
       </c>
       <c r="B7" t="n">
-        <v>93085</v>
+        <v>93087</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         <v>136859196</v>
       </c>
       <c r="B8" t="n">
-        <v>93085</v>
+        <v>93087</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>136859193</v>
       </c>
       <c r="B9" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>136859173</v>
       </c>
       <c r="B10" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>136859184</v>
       </c>
       <c r="B12" t="n">
-        <v>99697</v>
+        <v>99699</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
         <v>136859187</v>
       </c>
       <c r="B13" t="n">
-        <v>104882</v>
+        <v>104884</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 11553-2024 artfynd.xlsx
+++ b/artfynd/A 11553-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136859183</v>
       </c>
       <c r="B2" t="n">
-        <v>96573</v>
+        <v>96574</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136859192</v>
       </c>
       <c r="B3" t="n">
-        <v>96573</v>
+        <v>96574</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136859185</v>
       </c>
       <c r="B5" t="n">
-        <v>93087</v>
+        <v>93088</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>136859190</v>
       </c>
       <c r="B6" t="n">
-        <v>93087</v>
+        <v>93088</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1245,7 +1245,7 @@
         <v>136859191</v>
       </c>
       <c r="B7" t="n">
-        <v>93087</v>
+        <v>93088</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         <v>136859196</v>
       </c>
       <c r="B8" t="n">
-        <v>93087</v>
+        <v>93088</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>136859193</v>
       </c>
       <c r="B9" t="n">
-        <v>93451</v>
+        <v>93452</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>136859173</v>
       </c>
       <c r="B10" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>136859184</v>
       </c>
       <c r="B12" t="n">
-        <v>99699</v>
+        <v>99700</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
         <v>136859187</v>
       </c>
       <c r="B13" t="n">
-        <v>104884</v>
+        <v>104885</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 11553-2024 artfynd.xlsx
+++ b/artfynd/A 11553-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136859183</v>
       </c>
       <c r="B2" t="n">
-        <v>96574</v>
+        <v>96580</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136859192</v>
       </c>
       <c r="B3" t="n">
-        <v>96574</v>
+        <v>96580</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136859185</v>
       </c>
       <c r="B5" t="n">
-        <v>93088</v>
+        <v>93094</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>136859190</v>
       </c>
       <c r="B6" t="n">
-        <v>93088</v>
+        <v>93094</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1245,7 +1245,7 @@
         <v>136859191</v>
       </c>
       <c r="B7" t="n">
-        <v>93088</v>
+        <v>93094</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         <v>136859196</v>
       </c>
       <c r="B8" t="n">
-        <v>93088</v>
+        <v>93094</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>136859193</v>
       </c>
       <c r="B9" t="n">
-        <v>93452</v>
+        <v>93458</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>136859184</v>
       </c>
       <c r="B12" t="n">
-        <v>99700</v>
+        <v>99706</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
         <v>136859187</v>
       </c>
       <c r="B13" t="n">
-        <v>104885</v>
+        <v>104891</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 11553-2024 artfynd.xlsx
+++ b/artfynd/A 11553-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136859183</v>
       </c>
       <c r="B2" t="n">
-        <v>96580</v>
+        <v>96584</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136859192</v>
       </c>
       <c r="B3" t="n">
-        <v>96580</v>
+        <v>96584</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136859185</v>
       </c>
       <c r="B5" t="n">
-        <v>93094</v>
+        <v>93098</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>136859190</v>
       </c>
       <c r="B6" t="n">
-        <v>93094</v>
+        <v>93098</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1245,7 +1245,7 @@
         <v>136859191</v>
       </c>
       <c r="B7" t="n">
-        <v>93094</v>
+        <v>93098</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         <v>136859196</v>
       </c>
       <c r="B8" t="n">
-        <v>93094</v>
+        <v>93098</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>136859193</v>
       </c>
       <c r="B9" t="n">
-        <v>93458</v>
+        <v>93462</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>136859173</v>
       </c>
       <c r="B10" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>136859184</v>
       </c>
       <c r="B12" t="n">
-        <v>99706</v>
+        <v>99710</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
         <v>136859187</v>
       </c>
       <c r="B13" t="n">
-        <v>104891</v>
+        <v>104895</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 11553-2024 artfynd.xlsx
+++ b/artfynd/A 11553-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136859183</v>
       </c>
       <c r="B2" t="n">
-        <v>96584</v>
+        <v>96586</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136859192</v>
       </c>
       <c r="B3" t="n">
-        <v>96584</v>
+        <v>96586</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>136859184</v>
       </c>
       <c r="B12" t="n">
-        <v>99710</v>
+        <v>99712</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
         <v>136859187</v>
       </c>
       <c r="B13" t="n">
-        <v>104895</v>
+        <v>104897</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 11553-2024 artfynd.xlsx
+++ b/artfynd/A 11553-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136859183</v>
       </c>
       <c r="B2" t="n">
-        <v>96586</v>
+        <v>96588</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136859192</v>
       </c>
       <c r="B3" t="n">
-        <v>96586</v>
+        <v>96588</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136859185</v>
       </c>
       <c r="B5" t="n">
-        <v>93098</v>
+        <v>93100</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>136859190</v>
       </c>
       <c r="B6" t="n">
-        <v>93098</v>
+        <v>93100</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1245,7 +1245,7 @@
         <v>136859191</v>
       </c>
       <c r="B7" t="n">
-        <v>93098</v>
+        <v>93100</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         <v>136859196</v>
       </c>
       <c r="B8" t="n">
-        <v>93098</v>
+        <v>93100</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>136859193</v>
       </c>
       <c r="B9" t="n">
-        <v>93462</v>
+        <v>93464</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>136859173</v>
       </c>
       <c r="B10" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>136859184</v>
       </c>
       <c r="B12" t="n">
-        <v>99712</v>
+        <v>99714</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
         <v>136859187</v>
       </c>
       <c r="B13" t="n">
-        <v>104897</v>
+        <v>104899</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 11553-2024 artfynd.xlsx
+++ b/artfynd/A 11553-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136859183</v>
       </c>
       <c r="B2" t="n">
-        <v>96588</v>
+        <v>96601</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136859192</v>
       </c>
       <c r="B3" t="n">
-        <v>96588</v>
+        <v>96601</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136859185</v>
       </c>
       <c r="B5" t="n">
-        <v>93100</v>
+        <v>93113</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>136859190</v>
       </c>
       <c r="B6" t="n">
-        <v>93100</v>
+        <v>93113</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1245,7 +1245,7 @@
         <v>136859191</v>
       </c>
       <c r="B7" t="n">
-        <v>93100</v>
+        <v>93113</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         <v>136859196</v>
       </c>
       <c r="B8" t="n">
-        <v>93100</v>
+        <v>93113</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>136859193</v>
       </c>
       <c r="B9" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>136859173</v>
       </c>
       <c r="B10" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         <v>136859199</v>
       </c>
       <c r="B11" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>136859184</v>
       </c>
       <c r="B12" t="n">
-        <v>99714</v>
+        <v>99727</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
         <v>136859187</v>
       </c>
       <c r="B13" t="n">
-        <v>104899</v>
+        <v>104912</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 11553-2024 artfynd.xlsx
+++ b/artfynd/A 11553-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136859183</v>
       </c>
       <c r="B2" t="n">
-        <v>96601</v>
+        <v>96603</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136859192</v>
       </c>
       <c r="B3" t="n">
-        <v>96601</v>
+        <v>96603</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136859185</v>
       </c>
       <c r="B5" t="n">
-        <v>93113</v>
+        <v>93115</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>136859190</v>
       </c>
       <c r="B6" t="n">
-        <v>93113</v>
+        <v>93115</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1245,7 +1245,7 @@
         <v>136859191</v>
       </c>
       <c r="B7" t="n">
-        <v>93113</v>
+        <v>93115</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         <v>136859196</v>
       </c>
       <c r="B8" t="n">
-        <v>93113</v>
+        <v>93115</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>136859193</v>
       </c>
       <c r="B9" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>136859173</v>
       </c>
       <c r="B10" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         <v>136859199</v>
       </c>
       <c r="B11" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>136859184</v>
       </c>
       <c r="B12" t="n">
-        <v>99727</v>
+        <v>99729</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
         <v>136859187</v>
       </c>
       <c r="B13" t="n">
-        <v>104912</v>
+        <v>104914</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 11553-2024 artfynd.xlsx
+++ b/artfynd/A 11553-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136859183</v>
       </c>
       <c r="B2" t="n">
-        <v>96603</v>
+        <v>96606</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136859192</v>
       </c>
       <c r="B3" t="n">
-        <v>96603</v>
+        <v>96606</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136859185</v>
       </c>
       <c r="B5" t="n">
-        <v>93115</v>
+        <v>93118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>136859190</v>
       </c>
       <c r="B6" t="n">
-        <v>93115</v>
+        <v>93118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1245,7 +1245,7 @@
         <v>136859191</v>
       </c>
       <c r="B7" t="n">
-        <v>93115</v>
+        <v>93118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         <v>136859196</v>
       </c>
       <c r="B8" t="n">
-        <v>93115</v>
+        <v>93118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>136859193</v>
       </c>
       <c r="B9" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>136859184</v>
       </c>
       <c r="B12" t="n">
-        <v>99729</v>
+        <v>99732</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
         <v>136859187</v>
       </c>
       <c r="B13" t="n">
-        <v>104914</v>
+        <v>104917</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 11553-2024 artfynd.xlsx
+++ b/artfynd/A 11553-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136859183</v>
       </c>
       <c r="B2" t="n">
-        <v>96606</v>
+        <v>96616</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136859192</v>
       </c>
       <c r="B3" t="n">
-        <v>96606</v>
+        <v>96616</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136859185</v>
       </c>
       <c r="B5" t="n">
-        <v>93118</v>
+        <v>93128</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>136859190</v>
       </c>
       <c r="B6" t="n">
-        <v>93118</v>
+        <v>93128</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1245,7 +1245,7 @@
         <v>136859191</v>
       </c>
       <c r="B7" t="n">
-        <v>93118</v>
+        <v>93128</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         <v>136859196</v>
       </c>
       <c r="B8" t="n">
-        <v>93118</v>
+        <v>93128</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>136859193</v>
       </c>
       <c r="B9" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>136859173</v>
       </c>
       <c r="B10" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         <v>136859199</v>
       </c>
       <c r="B11" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>136859184</v>
       </c>
       <c r="B12" t="n">
-        <v>99732</v>
+        <v>99742</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
         <v>136859187</v>
       </c>
       <c r="B13" t="n">
-        <v>104917</v>
+        <v>104936</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 11553-2024 artfynd.xlsx
+++ b/artfynd/A 11553-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136859183</v>
       </c>
       <c r="B2" t="n">
-        <v>96616</v>
+        <v>96617</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136859192</v>
       </c>
       <c r="B3" t="n">
-        <v>96616</v>
+        <v>96617</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136859185</v>
       </c>
       <c r="B5" t="n">
-        <v>93128</v>
+        <v>93129</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>136859190</v>
       </c>
       <c r="B6" t="n">
-        <v>93128</v>
+        <v>93129</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1245,7 +1245,7 @@
         <v>136859191</v>
       </c>
       <c r="B7" t="n">
-        <v>93128</v>
+        <v>93129</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         <v>136859196</v>
       </c>
       <c r="B8" t="n">
-        <v>93128</v>
+        <v>93129</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>136859193</v>
       </c>
       <c r="B9" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>136859184</v>
       </c>
       <c r="B12" t="n">
-        <v>99742</v>
+        <v>99743</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
         <v>136859187</v>
       </c>
       <c r="B13" t="n">
-        <v>104936</v>
+        <v>104937</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 11553-2024 artfynd.xlsx
+++ b/artfynd/A 11553-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136859183</v>
       </c>
       <c r="B2" t="n">
-        <v>96617</v>
+        <v>96622</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136859192</v>
       </c>
       <c r="B3" t="n">
-        <v>96617</v>
+        <v>96622</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136859185</v>
       </c>
       <c r="B5" t="n">
-        <v>93129</v>
+        <v>93132</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>136859190</v>
       </c>
       <c r="B6" t="n">
-        <v>93129</v>
+        <v>93132</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1245,7 +1245,7 @@
         <v>136859191</v>
       </c>
       <c r="B7" t="n">
-        <v>93129</v>
+        <v>93132</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         <v>136859196</v>
       </c>
       <c r="B8" t="n">
-        <v>93129</v>
+        <v>93132</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>136859193</v>
       </c>
       <c r="B9" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>136859173</v>
       </c>
       <c r="B10" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         <v>136859199</v>
       </c>
       <c r="B11" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>136859184</v>
       </c>
       <c r="B12" t="n">
-        <v>99743</v>
+        <v>99748</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
         <v>136859187</v>
       </c>
       <c r="B13" t="n">
-        <v>104937</v>
+        <v>104942</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 11553-2024 artfynd.xlsx
+++ b/artfynd/A 11553-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136859183</v>
       </c>
       <c r="B2" t="n">
-        <v>96622</v>
+        <v>96624</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136859192</v>
       </c>
       <c r="B3" t="n">
-        <v>96622</v>
+        <v>96624</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136859185</v>
       </c>
       <c r="B5" t="n">
-        <v>93132</v>
+        <v>93134</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>136859190</v>
       </c>
       <c r="B6" t="n">
-        <v>93132</v>
+        <v>93134</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1245,7 +1245,7 @@
         <v>136859191</v>
       </c>
       <c r="B7" t="n">
-        <v>93132</v>
+        <v>93134</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         <v>136859196</v>
       </c>
       <c r="B8" t="n">
-        <v>93132</v>
+        <v>93134</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>136859193</v>
       </c>
       <c r="B9" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>136859184</v>
       </c>
       <c r="B12" t="n">
-        <v>99748</v>
+        <v>99751</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
         <v>136859187</v>
       </c>
       <c r="B13" t="n">
-        <v>104942</v>
+        <v>104945</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 11553-2024 artfynd.xlsx
+++ b/artfynd/A 11553-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136859183</v>
       </c>
       <c r="B2" t="n">
-        <v>96624</v>
+        <v>96630</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136859192</v>
       </c>
       <c r="B3" t="n">
-        <v>96624</v>
+        <v>96630</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136859185</v>
       </c>
       <c r="B5" t="n">
-        <v>93134</v>
+        <v>93140</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>136859190</v>
       </c>
       <c r="B6" t="n">
-        <v>93134</v>
+        <v>93140</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1245,7 +1245,7 @@
         <v>136859191</v>
       </c>
       <c r="B7" t="n">
-        <v>93134</v>
+        <v>93140</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         <v>136859196</v>
       </c>
       <c r="B8" t="n">
-        <v>93134</v>
+        <v>93140</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>136859193</v>
       </c>
       <c r="B9" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>136859173</v>
       </c>
       <c r="B10" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         <v>136859199</v>
       </c>
       <c r="B11" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>136859184</v>
       </c>
       <c r="B12" t="n">
-        <v>99751</v>
+        <v>99757</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
         <v>136859187</v>
       </c>
       <c r="B13" t="n">
-        <v>104945</v>
+        <v>104951</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 11553-2024 artfynd.xlsx
+++ b/artfynd/A 11553-2024 artfynd.xlsx
@@ -1926,7 +1926,7 @@
         <v>136859187</v>
       </c>
       <c r="B13" t="n">
-        <v>104951</v>
+        <v>104952</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 11553-2024 artfynd.xlsx
+++ b/artfynd/A 11553-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136859183</v>
       </c>
       <c r="B2" t="n">
-        <v>96630</v>
+        <v>96642</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136859192</v>
       </c>
       <c r="B3" t="n">
-        <v>96630</v>
+        <v>96642</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136859185</v>
       </c>
       <c r="B5" t="n">
-        <v>93140</v>
+        <v>93152</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>136859190</v>
       </c>
       <c r="B6" t="n">
-        <v>93140</v>
+        <v>93152</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1245,7 +1245,7 @@
         <v>136859191</v>
       </c>
       <c r="B7" t="n">
-        <v>93140</v>
+        <v>93152</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         <v>136859196</v>
       </c>
       <c r="B8" t="n">
-        <v>93140</v>
+        <v>93152</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>136859193</v>
       </c>
       <c r="B9" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>136859173</v>
       </c>
       <c r="B10" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>136859184</v>
       </c>
       <c r="B12" t="n">
-        <v>99757</v>
+        <v>99769</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
         <v>136859187</v>
       </c>
       <c r="B13" t="n">
-        <v>104952</v>
+        <v>104964</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
